--- a/runs/RELX/2026-10-14/bear/scratch/b_leverage_jun26_bbb/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/b_leverage_jun26_bbb/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2044.978683523766</v>
+        <v>2102.616855133198</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.1042</v>
+        <v>0.096248</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09600341328000001</v>
+        <v>0.08925455088000001</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11133.88536592723</v>
+        <v>11301.91868629803</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>37883.45022962111</v>
+        <v>41575.19596456885</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>25078.17596855731</v>
+        <v>28297.76144349687</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>36212.06133448454</v>
+        <v>39599.68012979489</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>29215.06133448454</v>
+        <v>32602.68012979489</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>28301.35887335375</v>
+        <v>31763.58542291601</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>16.23012596619258</v>
+        <v>18.21562684883034</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1623.012596619258</v>
+        <v>1821.562684883034</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.4142863238</v>
+        <v>-0.3426334591</v>
       </c>
     </row>
   </sheetData>
